--- a/rtss-mexico/src/main/resources/latinamerica/Latin-America-DemTrans-Curves.xlsx
+++ b/rtss-mexico/src/main/resources/latinamerica/Latin-America-DemTrans-Curves.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\latinamerica\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-mexico\src\main\resources\latinamerica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A4F197-8AAB-4084-82ED-0E5EF0669A87}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04854DDB-E7EA-4453-A7DC-214EF387030C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{9EAC7A11-4D1C-4B57-B029-05ECC1067029}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{9EAC7A11-4D1C-4B57-B029-05ECC1067029}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="35">
   <si>
     <t>Кривые демографического перехода латиноамериканских стран</t>
   </si>
@@ -131,10 +131,13 @@
     <t>Страницы CBR-14 и CDR-14 - по 14 странам</t>
   </si>
   <si>
-    <t>Лаг (в годах) оn D90 до падения relative CBR до 50%</t>
+    <t>Датировка начала перехода смертности и начала перехода рождаемости</t>
   </si>
   <si>
-    <t>Лаг (в годах) оn D90 до падения relative CBR до 90%</t>
+    <t>Лаг (в годах) оn D90 до B90 (падения relative CBR до 90%)</t>
+  </si>
+  <si>
+    <t>Лаг (в годах) оn D90 до B50 (падения relative CBR до 50%)</t>
   </si>
 </sst>
 </file>
@@ -312,7 +315,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
+          <a:endParaRPr lang="de-DE"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -13078,6 +13081,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -13085,7 +13089,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -25972,6 +25975,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -25979,7 +25983,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -27209,9 +27212,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -27249,7 +27252,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -27355,7 +27358,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -27497,7 +27500,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -27505,33 +27508,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC5A278-83B2-494A-B40C-E679082DAD40}">
-  <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D59"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.26171875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
         <v>29</v>
       </c>
@@ -27539,7 +27542,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" t="s">
         <v>21</v>
       </c>
@@ -27547,7 +27550,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" t="s">
         <v>24</v>
       </c>
@@ -27555,7 +27558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="s">
         <v>27</v>
       </c>
@@ -27563,7 +27566,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" t="s">
         <v>23</v>
       </c>
@@ -27571,7 +27574,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" t="s">
         <v>13</v>
       </c>
@@ -27579,7 +27582,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" t="s">
         <v>25</v>
       </c>
@@ -27587,7 +27590,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" t="s">
         <v>28</v>
       </c>
@@ -27595,7 +27598,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
         <v>8</v>
       </c>
@@ -27603,7 +27606,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" t="s">
         <v>22</v>
       </c>
@@ -27611,7 +27614,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" t="s">
         <v>16</v>
       </c>
@@ -27619,7 +27622,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" t="s">
         <v>26</v>
       </c>
@@ -27627,7 +27630,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" t="s">
         <v>12</v>
       </c>
@@ -27635,7 +27638,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" t="s">
         <v>4</v>
       </c>
@@ -27643,7 +27646,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" t="s">
         <v>17</v>
       </c>
@@ -27651,12 +27654,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
         <v>27</v>
       </c>
@@ -27664,7 +27667,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" t="s">
         <v>24</v>
       </c>
@@ -27672,7 +27675,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" t="s">
         <v>13</v>
       </c>
@@ -27680,7 +27683,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" t="s">
         <v>28</v>
       </c>
@@ -27688,7 +27691,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" t="s">
         <v>29</v>
       </c>
@@ -27696,7 +27699,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" t="s">
         <v>23</v>
       </c>
@@ -27704,7 +27707,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" t="s">
         <v>25</v>
       </c>
@@ -27712,7 +27715,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" t="s">
         <v>8</v>
       </c>
@@ -27720,7 +27723,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" t="s">
         <v>21</v>
       </c>
@@ -27728,7 +27731,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" t="s">
         <v>26</v>
       </c>
@@ -27736,7 +27739,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" t="s">
         <v>22</v>
       </c>
@@ -27744,7 +27747,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" t="s">
         <v>16</v>
       </c>
@@ -27752,7 +27755,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" t="s">
         <v>4</v>
       </c>
@@ -27760,7 +27763,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" t="s">
         <v>12</v>
       </c>
@@ -27768,12 +27771,171 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" t="s">
         <v>17</v>
       </c>
       <c r="C42">
         <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46">
+        <v>1885</v>
+      </c>
+      <c r="D46">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47">
+        <v>1893</v>
+      </c>
+      <c r="D47">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48">
+        <v>1921</v>
+      </c>
+      <c r="D48">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49">
+        <v>1948</v>
+      </c>
+      <c r="D49">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50">
+        <v>1948</v>
+      </c>
+      <c r="D50">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51">
+        <v>1922</v>
+      </c>
+      <c r="D51">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52">
+        <v>1923</v>
+      </c>
+      <c r="D52">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53">
+        <v>1916</v>
+      </c>
+      <c r="D53">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54">
+        <v>1949</v>
+      </c>
+      <c r="D54">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55">
+        <v>1913</v>
+      </c>
+      <c r="D55">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56">
+        <v>1940</v>
+      </c>
+      <c r="D56">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57">
+        <v>1938</v>
+      </c>
+      <c r="D57">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" t="s">
+        <v>29</v>
+      </c>
+      <c r="C58">
+        <v>1922</v>
+      </c>
+      <c r="D58">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59">
+        <v>1915</v>
+      </c>
+      <c r="D59">
+        <v>1969</v>
       </c>
     </row>
   </sheetData>
@@ -27787,28 +27949,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C0E91A8-8A66-4B4A-8B1A-D251E8C22352}">
   <dimension ref="A1:Q144"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.41796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.26171875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.41796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.26171875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.15625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.26171875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.26171875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.26171875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.41796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.68359375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.68359375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -27857,7 +28019,7 @@
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
@@ -27906,7 +28068,7 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
@@ -27955,7 +28117,7 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -27974,7 +28136,7 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -28027,7 +28189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="7">
         <v>0</v>
       </c>
@@ -28080,7 +28242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="7">
         <v>1</v>
       </c>
@@ -28133,7 +28295,7 @@
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="7">
         <v>2</v>
       </c>
@@ -28186,7 +28348,7 @@
         <v>1.0049999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="7">
         <v>3</v>
       </c>
@@ -28239,7 +28401,7 @@
         <v>1.006</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="7">
         <v>4</v>
       </c>
@@ -28292,7 +28454,7 @@
         <v>1.006</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="7">
         <v>5</v>
       </c>
@@ -28345,7 +28507,7 @@
         <v>1.0049999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="7">
         <v>6</v>
       </c>
@@ -28398,7 +28560,7 @@
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="7">
         <v>7</v>
       </c>
@@ -28451,7 +28613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="7">
         <v>8</v>
       </c>
@@ -28504,7 +28666,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="7">
         <v>9</v>
       </c>
@@ -28557,7 +28719,7 @@
         <v>0.99199999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="7">
         <v>10</v>
       </c>
@@ -28610,7 +28772,7 @@
         <v>0.98799999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="7">
         <v>11</v>
       </c>
@@ -28663,7 +28825,7 @@
         <v>0.98399999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="7">
         <v>12</v>
       </c>
@@ -28716,7 +28878,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="7">
         <v>13</v>
       </c>
@@ -28769,7 +28931,7 @@
         <v>0.97699999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="7">
         <v>14</v>
       </c>
@@ -28822,7 +28984,7 @@
         <v>0.97499999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="7">
         <v>15</v>
       </c>
@@ -28875,7 +29037,7 @@
         <v>0.97199999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="7">
         <v>16</v>
       </c>
@@ -28928,7 +29090,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="7">
         <v>17</v>
       </c>
@@ -28981,7 +29143,7 @@
         <v>0.96799999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="7">
         <v>18</v>
       </c>
@@ -29034,7 +29196,7 @@
         <v>0.96599999999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="7">
         <v>19</v>
       </c>
@@ -29087,7 +29249,7 @@
         <v>0.96399999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="7">
         <v>20</v>
       </c>
@@ -29140,7 +29302,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="7">
         <v>21</v>
       </c>
@@ -29193,7 +29355,7 @@
         <v>0.96099999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="7">
         <v>22</v>
       </c>
@@ -29246,7 +29408,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3">
         <v>23</v>
       </c>
@@ -29299,7 +29461,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3">
         <v>24</v>
       </c>
@@ -29352,7 +29514,7 @@
         <v>0.95899999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3">
         <v>25</v>
       </c>
@@ -29405,7 +29567,7 @@
         <v>0.95899999999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3">
         <v>26</v>
       </c>
@@ -29458,7 +29620,7 @@
         <v>0.95799999999999996</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3">
         <v>27</v>
       </c>
@@ -29511,7 +29673,7 @@
         <v>0.95599999999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3">
         <v>28</v>
       </c>
@@ -29564,7 +29726,7 @@
         <v>0.95399999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3">
         <v>29</v>
       </c>
@@ -29617,7 +29779,7 @@
         <v>0.95099999999999996</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3">
         <v>30</v>
       </c>
@@ -29670,7 +29832,7 @@
         <v>0.94799999999999995</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3">
         <v>31</v>
       </c>
@@ -29723,7 +29885,7 @@
         <v>0.94599999999999995</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3">
         <v>32</v>
       </c>
@@ -29776,7 +29938,7 @@
         <v>0.94299999999999995</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3">
         <v>33</v>
       </c>
@@ -29829,7 +29991,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="3">
         <v>34</v>
       </c>
@@ -29882,7 +30044,7 @@
         <v>0.93600000000000005</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="3">
         <v>35</v>
       </c>
@@ -29935,7 +30097,7 @@
         <v>0.93200000000000005</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="3">
         <v>36</v>
       </c>
@@ -29988,7 +30150,7 @@
         <v>0.92700000000000005</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="3">
         <v>37</v>
       </c>
@@ -30041,7 +30203,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="3">
         <v>38</v>
       </c>
@@ -30094,7 +30256,7 @@
         <v>0.91300000000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="3">
         <v>39</v>
       </c>
@@ -30147,7 +30309,7 @@
         <v>0.90400000000000003</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="3">
         <v>40</v>
       </c>
@@ -30200,7 +30362,7 @@
         <v>0.89500000000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="3">
         <v>41</v>
       </c>
@@ -30253,7 +30415,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="3">
         <v>42</v>
       </c>
@@ -30306,7 +30468,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="3">
         <v>43</v>
       </c>
@@ -30359,7 +30521,7 @@
         <v>0.86399999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="3">
         <v>44</v>
       </c>
@@ -30412,7 +30574,7 @@
         <v>0.85299999999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="3">
         <v>45</v>
       </c>
@@ -30465,7 +30627,7 @@
         <v>0.84199999999999997</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="3">
         <v>46</v>
       </c>
@@ -30518,7 +30680,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="3">
         <v>47</v>
       </c>
@@ -30571,7 +30733,7 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="3">
         <v>48</v>
       </c>
@@ -30624,7 +30786,7 @@
         <v>0.80500000000000005</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="3">
         <v>49</v>
       </c>
@@ -30677,7 +30839,7 @@
         <v>0.79300000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="3">
         <v>50</v>
       </c>
@@ -30730,7 +30892,7 @@
         <v>0.78200000000000003</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="3">
         <v>51</v>
       </c>
@@ -30783,7 +30945,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="3">
         <v>52</v>
       </c>
@@ -30836,7 +30998,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="3">
         <v>53</v>
       </c>
@@ -30889,7 +31051,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="3">
         <v>54</v>
       </c>
@@ -30942,7 +31104,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="3">
         <v>55</v>
       </c>
@@ -30995,7 +31157,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="3">
         <v>56</v>
       </c>
@@ -31048,7 +31210,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="3">
         <v>57</v>
       </c>
@@ -31101,7 +31263,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="3">
         <v>58</v>
       </c>
@@ -31154,7 +31316,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="3">
         <v>59</v>
       </c>
@@ -31207,7 +31369,7 @@
         <v>0.68899999999999995</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="3">
         <v>60</v>
       </c>
@@ -31260,7 +31422,7 @@
         <v>0.67800000000000005</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="3">
         <v>61</v>
       </c>
@@ -31313,7 +31475,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="3">
         <v>62</v>
       </c>
@@ -31366,7 +31528,7 @@
         <v>0.65700000000000003</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="3">
         <v>63</v>
       </c>
@@ -31419,7 +31581,7 @@
         <v>0.64700000000000002</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="3">
         <v>64</v>
       </c>
@@ -31472,7 +31634,7 @@
         <v>0.63800000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="3">
         <v>65</v>
       </c>
@@ -31525,7 +31687,7 @@
         <v>0.629</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="3">
         <v>66</v>
       </c>
@@ -31578,7 +31740,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="3">
         <v>67</v>
       </c>
@@ -31631,7 +31793,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="3">
         <v>68</v>
       </c>
@@ -31684,7 +31846,7 @@
         <v>0.60099999999999998</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="3">
         <v>69</v>
       </c>
@@ -31737,7 +31899,7 @@
         <v>0.59099999999999997</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="3">
         <v>70</v>
       </c>
@@ -31790,7 +31952,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="3">
         <v>71</v>
       </c>
@@ -31843,7 +32005,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="3">
         <v>72</v>
       </c>
@@ -31896,7 +32058,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="3">
         <v>73</v>
       </c>
@@ -31949,7 +32111,7 @@
         <v>0.55300000000000005</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="3">
         <v>74</v>
       </c>
@@ -32002,7 +32164,7 @@
         <v>0.54700000000000004</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="3">
         <v>75</v>
       </c>
@@ -32053,7 +32215,7 @@
         <v>0.54400000000000004</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="3">
         <v>76</v>
       </c>
@@ -32100,7 +32262,7 @@
         <v>0.54200000000000004</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="3">
         <v>77</v>
       </c>
@@ -32147,7 +32309,7 @@
         <v>0.53800000000000003</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="3">
         <v>78</v>
       </c>
@@ -32194,7 +32356,7 @@
         <v>0.53100000000000003</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="3">
         <v>79</v>
       </c>
@@ -32241,7 +32403,7 @@
         <v>0.52300000000000002</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="3">
         <v>80</v>
       </c>
@@ -32288,7 +32450,7 @@
         <v>0.51400000000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="3">
         <v>81</v>
       </c>
@@ -32335,7 +32497,7 @@
         <v>0.50700000000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="3">
         <v>82</v>
       </c>
@@ -32382,7 +32544,7 @@
         <v>0.501</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="3">
         <v>83</v>
       </c>
@@ -32429,7 +32591,7 @@
         <v>0.497</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="3">
         <v>84</v>
       </c>
@@ -32474,7 +32636,7 @@
         <v>0.496</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="3">
         <v>85</v>
       </c>
@@ -32519,7 +32681,7 @@
         <v>0.495</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="3">
         <v>86</v>
       </c>
@@ -32562,7 +32724,7 @@
         <v>0.49399999999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="3">
         <v>87</v>
       </c>
@@ -32605,7 +32767,7 @@
         <v>0.49099999999999999</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="3">
         <v>88</v>
       </c>
@@ -32648,7 +32810,7 @@
         <v>0.48699999999999999</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="3">
         <v>89</v>
       </c>
@@ -32691,7 +32853,7 @@
         <v>0.48099999999999998</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="3">
         <v>90</v>
       </c>
@@ -32734,7 +32896,7 @@
         <v>0.47499999999999998</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="3">
         <v>91</v>
       </c>
@@ -32777,7 +32939,7 @@
         <v>0.46800000000000003</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="3">
         <v>92</v>
       </c>
@@ -32820,7 +32982,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="3">
         <v>93</v>
       </c>
@@ -32863,7 +33025,7 @@
         <v>0.45200000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="3">
         <v>94</v>
       </c>
@@ -32906,7 +33068,7 @@
         <v>0.442</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="3">
         <v>95</v>
       </c>
@@ -32949,7 +33111,7 @@
         <v>0.432</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="3">
         <v>96</v>
       </c>
@@ -32992,7 +33154,7 @@
         <v>0.42099999999999999</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="3">
         <v>97</v>
       </c>
@@ -33035,7 +33197,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="3">
         <v>98</v>
       </c>
@@ -33078,7 +33240,7 @@
         <v>0.40200000000000002</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="3">
         <v>99</v>
       </c>
@@ -33121,7 +33283,7 @@
         <v>0.39700000000000002</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="3">
         <v>100</v>
       </c>
@@ -33164,7 +33326,7 @@
         <v>0.39800000000000002</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="3">
         <v>101</v>
       </c>
@@ -33205,7 +33367,7 @@
         <v>0.40500000000000003</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="3">
         <v>102</v>
       </c>
@@ -33242,7 +33404,7 @@
         <v>0.41499999999999998</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="3">
         <v>103</v>
       </c>
@@ -33277,7 +33439,7 @@
         <v>0.42199999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="3">
         <v>104</v>
       </c>
@@ -33312,7 +33474,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="3">
         <v>105</v>
       </c>
@@ -33347,7 +33509,7 @@
         <v>0.42299999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="3">
         <v>106</v>
       </c>
@@ -33382,7 +33544,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="3">
         <v>107</v>
       </c>
@@ -33417,7 +33579,7 @@
         <v>0.41699999999999998</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="3">
         <v>108</v>
       </c>
@@ -33450,7 +33612,7 @@
         <v>0.41599999999999998</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="3">
         <v>109</v>
       </c>
@@ -33481,7 +33643,7 @@
         <v>0.41699999999999998</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="3">
         <v>110</v>
       </c>
@@ -33512,7 +33674,7 @@
         <v>0.41499999999999998</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="3">
         <v>111</v>
       </c>
@@ -33541,7 +33703,7 @@
         <v>0.41199999999999998</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="3">
         <v>112</v>
       </c>
@@ -33570,7 +33732,7 @@
         <v>0.40699999999999997</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="3">
         <v>113</v>
       </c>
@@ -33599,7 +33761,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="3">
         <v>114</v>
       </c>
@@ -33628,7 +33790,7 @@
         <v>0.39300000000000002</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="3">
         <v>115</v>
       </c>
@@ -33657,7 +33819,7 @@
         <v>0.38600000000000001</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="3">
         <v>116</v>
       </c>
@@ -33686,7 +33848,7 @@
         <v>0.379</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="3">
         <v>117</v>
       </c>
@@ -33715,7 +33877,7 @@
         <v>0.373</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="3">
         <v>118</v>
       </c>
@@ -33744,7 +33906,7 @@
         <v>0.36899999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="3">
         <v>119</v>
       </c>
@@ -33773,7 +33935,7 @@
         <v>0.36499999999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="3">
         <v>120</v>
       </c>
@@ -33802,7 +33964,7 @@
         <v>0.36299999999999999</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="3">
         <v>121</v>
       </c>
@@ -33831,7 +33993,7 @@
         <v>0.36099999999999999</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="3">
         <v>122</v>
       </c>
@@ -33860,7 +34022,7 @@
         <v>0.35899999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="3">
         <v>123</v>
       </c>
@@ -33889,7 +34051,7 @@
         <v>0.35599999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="3">
         <v>124</v>
       </c>
@@ -33918,7 +34080,7 @@
         <v>0.35299999999999998</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="3">
         <v>125</v>
       </c>
@@ -33947,7 +34109,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="3">
         <v>126</v>
       </c>
@@ -33976,7 +34138,7 @@
         <v>0.34599999999999997</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="3">
         <v>127</v>
       </c>
@@ -34005,7 +34167,7 @@
         <v>0.34300000000000003</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="3">
         <v>128</v>
       </c>
@@ -34034,7 +34196,7 @@
         <v>0.34200000000000003</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="3">
         <v>129</v>
       </c>
@@ -34063,7 +34225,7 @@
         <v>0.34300000000000003</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="3">
         <v>130</v>
       </c>
@@ -34092,7 +34254,7 @@
         <v>0.34599999999999997</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="3">
         <v>131</v>
       </c>
@@ -34119,7 +34281,7 @@
         <v>0.34899999999999998</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="3">
         <v>132</v>
       </c>
@@ -34146,7 +34308,7 @@
         <v>0.34499999999999997</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="3">
         <v>133</v>
       </c>
@@ -34173,7 +34335,7 @@
         <v>0.33400000000000002</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="3">
         <v>134</v>
       </c>
@@ -34200,7 +34362,7 @@
         <v>0.317</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="3">
         <v>135</v>
       </c>
@@ -34227,7 +34389,7 @@
         <v>0.29899999999999999</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="3">
         <v>136</v>
       </c>
@@ -34254,7 +34416,7 @@
         <v>0.28100000000000003</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="3">
         <v>137</v>
       </c>
@@ -34281,7 +34443,7 @@
         <v>0.26300000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="3">
         <v>138</v>
       </c>
@@ -34318,28 +34480,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62CC78C-7ACC-463F-B4CA-4716895C0AF9}">
   <dimension ref="A1:Q144"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.41796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.26171875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.41796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.26171875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.15625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.26171875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.26171875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.26171875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.41796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.68359375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.68359375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -34388,7 +34550,7 @@
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
@@ -34437,7 +34599,7 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
@@ -34486,7 +34648,7 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -34505,7 +34667,7 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>21</v>
@@ -34556,7 +34718,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3">
         <v>0</v>
       </c>
@@ -34609,7 +34771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -34662,7 +34824,7 @@
         <v>0.97899999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -34715,7 +34877,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -34768,7 +34930,7 @@
         <v>0.94099999999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3">
         <v>4</v>
       </c>
@@ -34821,7 +34983,7 @@
         <v>0.92300000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -34874,7 +35036,7 @@
         <v>0.90600000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3">
         <v>6</v>
       </c>
@@ -34927,7 +35089,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3">
         <v>7</v>
       </c>
@@ -34980,7 +35142,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3">
         <v>8</v>
       </c>
@@ -35033,7 +35195,7 @@
         <v>0.86199999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3">
         <v>9</v>
       </c>
@@ -35086,7 +35248,7 @@
         <v>0.84899999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3">
         <v>10</v>
       </c>
@@ -35139,7 +35301,7 @@
         <v>0.83599999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3">
         <v>11</v>
       </c>
@@ -35192,7 +35354,7 @@
         <v>0.82399999999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3">
         <v>12</v>
       </c>
@@ -35245,7 +35407,7 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3">
         <v>13</v>
       </c>
@@ -35298,7 +35460,7 @@
         <v>0.79700000000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3">
         <v>14</v>
       </c>
@@ -35351,7 +35513,7 @@
         <v>0.78400000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3">
         <v>15</v>
       </c>
@@ -35404,7 +35566,7 @@
         <v>0.77100000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3">
         <v>16</v>
       </c>
@@ -35457,7 +35619,7 @@
         <v>0.75700000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3">
         <v>17</v>
       </c>
@@ -35510,7 +35672,7 @@
         <v>0.74399999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3">
         <v>18</v>
       </c>
@@ -35563,7 +35725,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3">
         <v>19</v>
       </c>
@@ -35616,7 +35778,7 @@
         <v>0.71699999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3">
         <v>20</v>
       </c>
@@ -35669,7 +35831,7 @@
         <v>0.70299999999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3">
         <v>21</v>
       </c>
@@ -35722,7 +35884,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3">
         <v>22</v>
       </c>
@@ -35775,7 +35937,7 @@
         <v>0.67600000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3">
         <v>23</v>
       </c>
@@ -35828,7 +35990,7 @@
         <v>0.66200000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3">
         <v>24</v>
       </c>
@@ -35881,7 +36043,7 @@
         <v>0.64800000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3">
         <v>25</v>
       </c>
@@ -35934,7 +36096,7 @@
         <v>0.63400000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3">
         <v>26</v>
       </c>
@@ -35987,7 +36149,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3">
         <v>27</v>
       </c>
@@ -36040,7 +36202,7 @@
         <v>0.60599999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3">
         <v>28</v>
       </c>
@@ -36093,7 +36255,7 @@
         <v>0.59099999999999997</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3">
         <v>29</v>
       </c>
@@ -36146,7 +36308,7 @@
         <v>0.57599999999999996</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3">
         <v>30</v>
       </c>
@@ -36199,7 +36361,7 @@
         <v>0.56100000000000005</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3">
         <v>31</v>
       </c>
@@ -36252,7 +36414,7 @@
         <v>0.54600000000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3">
         <v>32</v>
       </c>
@@ -36305,7 +36467,7 @@
         <v>0.53300000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3">
         <v>33</v>
       </c>
@@ -36358,7 +36520,7 @@
         <v>0.51900000000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="3">
         <v>34</v>
       </c>
@@ -36411,7 +36573,7 @@
         <v>0.50600000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="3">
         <v>35</v>
       </c>
@@ -36464,7 +36626,7 @@
         <v>0.49199999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="3">
         <v>36</v>
       </c>
@@ -36517,7 +36679,7 @@
         <v>0.47899999999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="3">
         <v>37</v>
       </c>
@@ -36570,7 +36732,7 @@
         <v>0.46600000000000003</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="3">
         <v>38</v>
       </c>
@@ -36623,7 +36785,7 @@
         <v>0.45400000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="3">
         <v>39</v>
       </c>
@@ -36676,7 +36838,7 @@
         <v>0.44400000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="3">
         <v>40</v>
       </c>
@@ -36729,7 +36891,7 @@
         <v>0.434</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="3">
         <v>41</v>
       </c>
@@ -36782,7 +36944,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="3">
         <v>42</v>
       </c>
@@ -36835,7 +36997,7 @@
         <v>0.41599999999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="3">
         <v>43</v>
       </c>
@@ -36888,7 +37050,7 @@
         <v>0.40699999999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="3">
         <v>44</v>
       </c>
@@ -36941,7 +37103,7 @@
         <v>0.39700000000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="3">
         <v>45</v>
       </c>
@@ -36994,7 +37156,7 @@
         <v>0.38600000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="3">
         <v>46</v>
       </c>
@@ -37047,7 +37209,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="3">
         <v>47</v>
       </c>
@@ -37100,7 +37262,7 @@
         <v>0.36499999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="3">
         <v>48</v>
       </c>
@@ -37153,7 +37315,7 @@
         <v>0.35399999999999998</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="3">
         <v>49</v>
       </c>
@@ -37206,7 +37368,7 @@
         <v>0.34499999999999997</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="3">
         <v>50</v>
       </c>
@@ -37259,7 +37421,7 @@
         <v>0.33500000000000002</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="3">
         <v>51</v>
       </c>
@@ -37312,7 +37474,7 @@
         <v>0.32700000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="3">
         <v>52</v>
       </c>
@@ -37365,7 +37527,7 @@
         <v>0.318</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="3">
         <v>53</v>
       </c>
@@ -37418,7 +37580,7 @@
         <v>0.309</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="3">
         <v>54</v>
       </c>
@@ -37471,7 +37633,7 @@
         <v>0.30099999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="3">
         <v>55</v>
       </c>
@@ -37524,7 +37686,7 @@
         <v>0.29199999999999998</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="3">
         <v>56</v>
       </c>
@@ -37577,7 +37739,7 @@
         <v>0.28399999999999997</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="3">
         <v>57</v>
       </c>
@@ -37630,7 +37792,7 @@
         <v>0.27600000000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="3">
         <v>58</v>
       </c>
@@ -37683,7 +37845,7 @@
         <v>0.26900000000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="3">
         <v>59</v>
       </c>
@@ -37736,7 +37898,7 @@
         <v>0.26200000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="3">
         <v>60</v>
       </c>
@@ -37789,7 +37951,7 @@
         <v>0.25600000000000001</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="3">
         <v>61</v>
       </c>
@@ -37842,7 +38004,7 @@
         <v>0.251</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="3">
         <v>62</v>
       </c>
@@ -37895,7 +38057,7 @@
         <v>0.246</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="3">
         <v>63</v>
       </c>
@@ -37948,7 +38110,7 @@
         <v>0.24099999999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="3">
         <v>64</v>
       </c>
@@ -38001,7 +38163,7 @@
         <v>0.23699999999999999</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="3">
         <v>65</v>
       </c>
@@ -38054,7 +38216,7 @@
         <v>0.23400000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="3">
         <v>66</v>
       </c>
@@ -38107,7 +38269,7 @@
         <v>0.23100000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="3">
         <v>67</v>
       </c>
@@ -38160,7 +38322,7 @@
         <v>0.22900000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="3">
         <v>68</v>
       </c>
@@ -38213,7 +38375,7 @@
         <v>0.22700000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="3">
         <v>69</v>
       </c>
@@ -38266,7 +38428,7 @@
         <v>0.22600000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="3">
         <v>70</v>
       </c>
@@ -38319,7 +38481,7 @@
         <v>0.224</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="3">
         <v>71</v>
       </c>
@@ -38372,7 +38534,7 @@
         <v>0.222</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="3">
         <v>72</v>
       </c>
@@ -38425,7 +38587,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="3">
         <v>73</v>
       </c>
@@ -38478,7 +38640,7 @@
         <v>0.219</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="3">
         <v>74</v>
       </c>
@@ -38531,7 +38693,7 @@
         <v>0.219</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="3">
         <v>75</v>
       </c>
@@ -38582,7 +38744,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="3">
         <v>76</v>
       </c>
@@ -38629,7 +38791,7 @@
         <v>0.221</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="3">
         <v>77</v>
       </c>
@@ -38676,7 +38838,7 @@
         <v>0.223</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="3">
         <v>78</v>
       </c>
@@ -38723,7 +38885,7 @@
         <v>0.224</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="3">
         <v>79</v>
       </c>
@@ -38770,7 +38932,7 @@
         <v>0.223</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="3">
         <v>80</v>
       </c>
@@ -38817,7 +38979,7 @@
         <v>0.223</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="3">
         <v>81</v>
       </c>
@@ -38864,7 +39026,7 @@
         <v>0.222</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="3">
         <v>82</v>
       </c>
@@ -38911,7 +39073,7 @@
         <v>0.222</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="3">
         <v>83</v>
       </c>
@@ -38958,7 +39120,7 @@
         <v>0.221</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="3">
         <v>84</v>
       </c>
@@ -39003,7 +39165,7 @@
         <v>0.221</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="3">
         <v>85</v>
       </c>
@@ -39048,7 +39210,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="3">
         <v>86</v>
       </c>
@@ -39091,7 +39253,7 @@
         <v>0.219</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="3">
         <v>87</v>
       </c>
@@ -39134,7 +39296,7 @@
         <v>0.218</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="3">
         <v>88</v>
       </c>
@@ -39177,7 +39339,7 @@
         <v>0.217</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="3">
         <v>89</v>
       </c>
@@ -39220,7 +39382,7 @@
         <v>0.216</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="3">
         <v>90</v>
       </c>
@@ -39263,7 +39425,7 @@
         <v>0.216</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="3">
         <v>91</v>
       </c>
@@ -39306,7 +39468,7 @@
         <v>0.216</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="3">
         <v>92</v>
       </c>
@@ -39349,7 +39511,7 @@
         <v>0.217</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="3">
         <v>93</v>
       </c>
@@ -39392,7 +39554,7 @@
         <v>0.218</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="3">
         <v>94</v>
       </c>
@@ -39435,7 +39597,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="3">
         <v>95</v>
       </c>
@@ -39478,7 +39640,7 @@
         <v>0.221</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="3">
         <v>96</v>
       </c>
@@ -39521,7 +39683,7 @@
         <v>0.223</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="3">
         <v>97</v>
       </c>
@@ -39564,7 +39726,7 @@
         <v>0.224</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="3">
         <v>98</v>
       </c>
@@ -39607,7 +39769,7 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="3">
         <v>99</v>
       </c>
@@ -39650,7 +39812,7 @@
         <v>0.22600000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="3">
         <v>100</v>
       </c>
@@ -39693,7 +39855,7 @@
         <v>0.22700000000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="3">
         <v>101</v>
       </c>
@@ -39734,7 +39896,7 @@
         <v>0.22700000000000001</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="3">
         <v>102</v>
       </c>
@@ -39771,7 +39933,7 @@
         <v>0.22600000000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="3">
         <v>103</v>
       </c>
@@ -39806,7 +39968,7 @@
         <v>0.223</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="3">
         <v>104</v>
       </c>
@@ -39841,7 +40003,7 @@
         <v>0.221</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="3">
         <v>105</v>
       </c>
@@ -39876,7 +40038,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="3">
         <v>106</v>
       </c>
@@ -39911,7 +40073,7 @@
         <v>0.221</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="3">
         <v>107</v>
       </c>
@@ -39946,7 +40108,7 @@
         <v>0.224</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="3">
         <v>108</v>
       </c>
@@ -39979,7 +40141,7 @@
         <v>0.22800000000000001</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="3">
         <v>109</v>
       </c>
@@ -40010,7 +40172,7 @@
         <v>0.23300000000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="3">
         <v>110</v>
       </c>
@@ -40041,7 +40203,7 @@
         <v>0.23499999999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="3">
         <v>111</v>
       </c>
@@ -40070,7 +40232,7 @@
         <v>0.23499999999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="3">
         <v>112</v>
       </c>
@@ -40099,7 +40261,7 @@
         <v>0.23400000000000001</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="3">
         <v>113</v>
       </c>
@@ -40128,7 +40290,7 @@
         <v>0.23300000000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="3">
         <v>114</v>
       </c>
@@ -40157,7 +40319,7 @@
         <v>0.23300000000000001</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="3">
         <v>115</v>
       </c>
@@ -40186,7 +40348,7 @@
         <v>0.23200000000000001</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="3">
         <v>116</v>
       </c>
@@ -40215,7 +40377,7 @@
         <v>0.23200000000000001</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="3">
         <v>117</v>
       </c>
@@ -40244,7 +40406,7 @@
         <v>0.23200000000000001</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="3">
         <v>118</v>
       </c>
@@ -40273,7 +40435,7 @@
         <v>0.23200000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="3">
         <v>119</v>
       </c>
@@ -40302,7 +40464,7 @@
         <v>0.23200000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="3">
         <v>120</v>
       </c>
@@ -40331,7 +40493,7 @@
         <v>0.23300000000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="3">
         <v>121</v>
       </c>
@@ -40360,7 +40522,7 @@
         <v>0.23400000000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="3">
         <v>122</v>
       </c>
@@ -40389,7 +40551,7 @@
         <v>0.23599999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="3">
         <v>123</v>
       </c>
@@ -40418,7 +40580,7 @@
         <v>0.23799999999999999</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="3">
         <v>124</v>
       </c>
@@ -40447,7 +40609,7 @@
         <v>0.23899999999999999</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="3">
         <v>125</v>
       </c>
@@ -40476,7 +40638,7 @@
         <v>0.24099999999999999</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="3">
         <v>126</v>
       </c>
@@ -40505,7 +40667,7 @@
         <v>0.24399999999999999</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="3">
         <v>127</v>
       </c>
@@ -40534,7 +40696,7 @@
         <v>0.247</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="3">
         <v>128</v>
       </c>
@@ -40563,7 +40725,7 @@
         <v>0.251</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="3">
         <v>129</v>
       </c>
@@ -40592,7 +40754,7 @@
         <v>0.255</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="3">
         <v>130</v>
       </c>
@@ -40621,7 +40783,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="3">
         <v>131</v>
       </c>
@@ -40648,7 +40810,7 @@
         <v>0.26500000000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="3">
         <v>132</v>
       </c>
@@ -40675,7 +40837,7 @@
         <v>0.26900000000000002</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="3">
         <v>133</v>
       </c>
@@ -40702,7 +40864,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="3">
         <v>134</v>
       </c>
@@ -40729,7 +40891,7 @@
         <v>0.27100000000000002</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="3">
         <v>135</v>
       </c>
@@ -40756,7 +40918,7 @@
         <v>0.27200000000000002</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="3">
         <v>136</v>
       </c>
@@ -40783,7 +40945,7 @@
         <v>0.27200000000000002</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="3">
         <v>137</v>
       </c>
@@ -40810,7 +40972,7 @@
         <v>0.27100000000000002</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="3">
         <v>138</v>
       </c>
@@ -40842,4 +41004,10 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/rtss-mexico/src/main/resources/latinamerica/Latin-America-DemTrans-Curves.xlsx
+++ b/rtss-mexico/src/main/resources/latinamerica/Latin-America-DemTrans-Curves.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-mexico\src\main\resources\latinamerica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04854DDB-E7EA-4453-A7DC-214EF387030C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47A0596-2433-47ED-8FCD-910A749EA95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{9EAC7A11-4D1C-4B57-B029-05ECC1067029}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="48">
   <si>
     <t>Кривые демографического перехода латиноамериканских стран</t>
   </si>
@@ -131,13 +131,63 @@
     <t>Страницы CBR-14 и CDR-14 - по 14 странам</t>
   </si>
   <si>
-    <t>Датировка начала перехода смертности и начала перехода рождаемости</t>
-  </si>
-  <si>
     <t>Лаг (в годах) оn D90 до B90 (падения relative CBR до 90%)</t>
   </si>
   <si>
     <t>Лаг (в годах) оn D90 до B50 (падения relative CBR до 50%)</t>
+  </si>
+  <si>
+    <t>Датировка начала перехода смертности (D90), начала перехода рождаемости (B90) и конца главной фазы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">т.е. года падения естественного прироста обратно к значению в точке D90 </t>
+  </si>
+  <si>
+    <t>D90</t>
+  </si>
+  <si>
+    <t>B90</t>
+  </si>
+  <si>
+    <t>КГФ</t>
+  </si>
+  <si>
+    <t>Длительность главной фазы с начала перехода D90 и до падения естественного прироста обратно к значению в точке D90 (годы),</t>
+  </si>
+  <si>
+    <t>естественный рост населения (разы сверх начального 1.0) за период главной фазы</t>
+  </si>
+  <si>
+    <t>страна</t>
+  </si>
+  <si>
+    <t>макс. еп.
+в главной
+фазе</t>
+  </si>
+  <si>
+    <t>длительность
+главной 
+фазы
+(лет)</t>
+  </si>
+  <si>
+    <t>еп
+в год
+D90</t>
+  </si>
+  <si>
+    <t>рост
+населения
+(разы)
+за главную
+фазу</t>
+  </si>
+  <si>
+    <t>величина годового естественного прироста в точке D90 (промилле),</t>
+  </si>
+  <si>
+    <t>максимальная величина годового естественного прироста в главной фазе (промилле),</t>
   </si>
 </sst>
 </file>
@@ -173,12 +223,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -193,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -212,6 +268,13 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -27508,10 +27571,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC5A278-83B2-494A-B40C-E679082DAD40}">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="16.26171875" customWidth="1"/>
+    <col min="2" max="2" width="11.26171875" customWidth="1"/>
+    <col min="3" max="3" width="12.83984375" customWidth="1"/>
+    <col min="6" max="6" width="10.68359375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.75">
@@ -27531,7 +27596,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27656,7 +27721,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27699,7 +27764,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" t="s">
         <v>23</v>
       </c>
@@ -27707,7 +27772,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" t="s">
         <v>25</v>
       </c>
@@ -27715,7 +27780,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" t="s">
         <v>8</v>
       </c>
@@ -27723,7 +27788,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" t="s">
         <v>21</v>
       </c>
@@ -27731,7 +27796,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" t="s">
         <v>26</v>
       </c>
@@ -27739,7 +27804,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" t="s">
         <v>22</v>
       </c>
@@ -27747,7 +27812,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" t="s">
         <v>16</v>
       </c>
@@ -27755,7 +27820,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" t="s">
         <v>4</v>
       </c>
@@ -27763,7 +27828,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" t="s">
         <v>12</v>
       </c>
@@ -27771,7 +27836,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" t="s">
         <v>17</v>
       </c>
@@ -27779,163 +27844,499 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" t="s">
         <v>21</v>
       </c>
-      <c r="C46">
+      <c r="C48" s="3">
         <v>1885</v>
       </c>
-      <c r="D46">
+      <c r="D48" s="3">
         <v>1903</v>
       </c>
+      <c r="E48" s="3">
+        <v>1978</v>
+      </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" t="s">
         <v>4</v>
       </c>
-      <c r="C47">
+      <c r="C49" s="3">
         <v>1893</v>
       </c>
-      <c r="D47">
+      <c r="D49" s="3">
         <v>1960</v>
       </c>
+      <c r="E49" s="3">
+        <v>1992</v>
+      </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" t="s">
         <v>22</v>
       </c>
-      <c r="C48">
+      <c r="C50" s="3">
         <v>1921</v>
       </c>
-      <c r="D48">
+      <c r="D50" s="3">
         <v>1972</v>
       </c>
+      <c r="E50" s="3">
+        <v>2012</v>
+      </c>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" t="s">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" t="s">
         <v>23</v>
       </c>
-      <c r="C49">
+      <c r="C51" s="3">
         <v>1948</v>
       </c>
-      <c r="D49">
+      <c r="D51" s="3">
         <v>1978</v>
       </c>
+      <c r="E51" s="3">
+        <v>2013</v>
+      </c>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" t="s">
         <v>24</v>
       </c>
-      <c r="C50">
+      <c r="C52" s="3">
         <v>1948</v>
       </c>
-      <c r="D50">
+      <c r="D52" s="3">
         <v>1966</v>
       </c>
+      <c r="E52" s="3">
+        <v>2005</v>
+      </c>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" t="s">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" t="s">
         <v>8</v>
       </c>
-      <c r="C51">
+      <c r="C53" s="3">
         <v>1922</v>
       </c>
-      <c r="D51">
+      <c r="D53" s="3">
         <v>1967</v>
       </c>
+      <c r="E53" s="3">
+        <v>1991</v>
+      </c>
     </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" t="s">
         <v>25</v>
       </c>
-      <c r="C52">
+      <c r="C54" s="3">
         <v>1923</v>
       </c>
-      <c r="D52">
+      <c r="D54" s="3">
         <v>1963</v>
       </c>
+      <c r="E54" s="3">
+        <v>1994</v>
+      </c>
     </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" t="s">
         <v>26</v>
       </c>
-      <c r="C53">
+      <c r="C55" s="3">
         <v>1916</v>
       </c>
-      <c r="D53">
+      <c r="D55" s="3">
         <v>1974</v>
       </c>
+      <c r="E55" s="3">
+        <v>2013</v>
+      </c>
     </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" t="s">
         <v>27</v>
       </c>
-      <c r="C54">
+      <c r="C56" s="3">
         <v>1949</v>
       </c>
-      <c r="D54">
+      <c r="D56" s="3">
         <v>1972</v>
       </c>
+      <c r="E56" s="3">
+        <v>1997</v>
+      </c>
     </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" t="s">
         <v>12</v>
       </c>
-      <c r="C55">
+      <c r="C57" s="3">
         <v>1913</v>
       </c>
-      <c r="D55">
+      <c r="D57" s="3">
         <v>1972</v>
       </c>
+      <c r="E57" s="3">
+        <v>1991</v>
+      </c>
     </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" t="s">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" t="s">
         <v>13</v>
       </c>
-      <c r="C56">
+      <c r="C58" s="3">
         <v>1940</v>
       </c>
-      <c r="D56">
+      <c r="D58" s="3">
         <v>1974</v>
       </c>
+      <c r="E58" s="3">
+        <v>2008</v>
+      </c>
     </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" t="s">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" t="s">
         <v>28</v>
       </c>
-      <c r="C57">
+      <c r="C59" s="3">
         <v>1938</v>
       </c>
-      <c r="D57">
+      <c r="D59" s="3">
         <v>1979</v>
       </c>
+      <c r="E59" s="3">
+        <v>2004</v>
+      </c>
     </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" t="s">
         <v>29</v>
       </c>
-      <c r="C58">
+      <c r="C60" s="3">
         <v>1922</v>
       </c>
-      <c r="D58">
+      <c r="D60" s="3">
         <v>1937</v>
       </c>
+      <c r="E60" s="3">
+        <v>2001</v>
+      </c>
     </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" t="s">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" t="s">
         <v>16</v>
       </c>
-      <c r="C59">
+      <c r="C61" s="3">
         <v>1915</v>
       </c>
-      <c r="D59">
+      <c r="D61" s="3">
         <v>1969</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69" s="3">
+        <v>93</v>
+      </c>
+      <c r="D69" s="10">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E69" s="10">
+        <v>36.6</v>
+      </c>
+      <c r="F69" s="10">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="3">
+        <v>99</v>
+      </c>
+      <c r="D70" s="10">
+        <v>17</v>
+      </c>
+      <c r="E70" s="10">
+        <v>39.5</v>
+      </c>
+      <c r="F70" s="10">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" s="3">
+        <v>91</v>
+      </c>
+      <c r="D71" s="10">
+        <v>14.3</v>
+      </c>
+      <c r="E71" s="10">
+        <v>35.6</v>
+      </c>
+      <c r="F71" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" s="3">
+        <v>65</v>
+      </c>
+      <c r="D72" s="10">
+        <v>21.8</v>
+      </c>
+      <c r="E72" s="10">
+        <v>43.4</v>
+      </c>
+      <c r="F72" s="10">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="3">
+        <v>57</v>
+      </c>
+      <c r="D73" s="10">
+        <v>25.1</v>
+      </c>
+      <c r="E73" s="10">
+        <v>47.8</v>
+      </c>
+      <c r="F73" s="10">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="3">
+        <v>69</v>
+      </c>
+      <c r="D74" s="10">
+        <v>20.9</v>
+      </c>
+      <c r="E74" s="10">
+        <v>38.9</v>
+      </c>
+      <c r="F74" s="10">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" s="3">
+        <v>71</v>
+      </c>
+      <c r="D75" s="10">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="E75" s="10">
+        <v>42.8</v>
+      </c>
+      <c r="F75" s="10">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" s="3">
+        <v>97</v>
+      </c>
+      <c r="D76" s="10">
+        <v>14.1</v>
+      </c>
+      <c r="E76" s="10">
+        <v>40.5</v>
+      </c>
+      <c r="F76" s="10">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77" s="3">
+        <v>48</v>
+      </c>
+      <c r="D77" s="10">
+        <v>24.6</v>
+      </c>
+      <c r="E77" s="10">
+        <v>45.6</v>
+      </c>
+      <c r="F77" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="3">
+        <v>78</v>
+      </c>
+      <c r="D78" s="10">
+        <v>21.4</v>
+      </c>
+      <c r="E78" s="10">
+        <v>35.1</v>
+      </c>
+      <c r="F78" s="10">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" s="3">
+        <v>68</v>
+      </c>
+      <c r="D79" s="10">
+        <v>14.6</v>
+      </c>
+      <c r="E79" s="10">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="F79" s="10">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" t="s">
+        <v>28</v>
+      </c>
+      <c r="C80" s="3">
+        <v>66</v>
+      </c>
+      <c r="D80" s="10">
+        <v>16.7</v>
+      </c>
+      <c r="E80" s="10">
+        <v>37.4</v>
+      </c>
+      <c r="F80" s="10">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" s="3">
+        <v>79</v>
+      </c>
+      <c r="D81" s="10">
+        <v>11.3</v>
+      </c>
+      <c r="E81" s="10">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="F81" s="10">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" s="3">
+        <v>98</v>
+      </c>
+      <c r="D82" s="10">
+        <v>15.8</v>
+      </c>
+      <c r="E82" s="10">
+        <v>41.5</v>
+      </c>
+      <c r="F82" s="10">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
